--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_2_R1.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_2_R1.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5794</v>
+        <v>3.4456</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3109</v>
+        <v>5.5469</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7316</v>
+        <v>-2.1013</v>
       </c>
       <c r="G2" t="n">
         <v>5.6927</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5671</v>
+        <v>0.4334</v>
       </c>
       <c r="T2" t="n">
-        <v>0.13</v>
+        <v>0.3659</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4371</v>
+        <v>0.0674</v>
       </c>
       <c r="V2" t="n">
         <v>-2.6805</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6561</v>
+        <v>3.233</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3927</v>
+        <v>4.6599</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7365</v>
+        <v>-1.4268</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3893</v>
+        <v>2.3027</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.474</v>
+        <v>0.0108</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8633</v>
+        <v>2.292</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0581</v>
+        <v>2.6498</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1379</v>
+        <v>0.6659</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9201</v>
+        <v>1.984</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6687</v>
+        <v>-0.3471</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.612</v>
+        <v>-0.6551</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0568</v>
+        <v>0.308</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0375</v>
+        <v>-1.7682</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4248</v>
+        <v>0.1852</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3873</v>
+        <v>-1.9533</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9304</v>
+        <v>2.0026</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1418</v>
+        <v>3.2166</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9019</v>
+        <v>1.1015</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3624</v>
+        <v>0.6741</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4604</v>
+        <v>0.4274</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3027</v>
+        <v>1.4347</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0108</v>
+        <v>0.0663</v>
       </c>
       <c r="I4" t="n">
-        <v>2.292</v>
+        <v>1.3684</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6498</v>
+        <v>1.2241</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6659</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.984</v>
+        <v>0.5351</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3471</v>
+        <v>0.2106</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6551</v>
+        <v>-0.6227</v>
       </c>
       <c r="O4" t="n">
-        <v>0.308</v>
+        <v>0.8333</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.0993</v>
+        <v>-0.3332</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1123</v>
+        <v>0.8417</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.9869</v>
+        <v>-1.1749</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0026</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2023</v>
+        <v>0.7524</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6741</v>
+        <v>2.6234</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5282</v>
+        <v>-1.871</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4347</v>
+        <v>0.3893</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0663</v>
+        <v>-0.474</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3684</v>
+        <v>0.8633</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2241</v>
+        <v>1.0581</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.1379</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5351</v>
+        <v>0.9201</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2106</v>
+        <v>-0.6687</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6227</v>
+        <v>-0.612</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8333</v>
+        <v>-0.0568</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2324</v>
+        <v>0.1338</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8417</v>
+        <v>1.6555</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0741</v>
+        <v>-1.5217</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4931</v>
+        <v>0.4767</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2533</v>
+        <v>1.3713</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7602</v>
+        <v>-0.8946</v>
       </c>
       <c r="G6" t="n">
         <v>1.3641</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7266</v>
+        <v>-0.7431</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4402</v>
+        <v>-0.3222</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2864</v>
+        <v>-0.4208</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2447</v>
+        <v>0.1573</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7575</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.5128</v>
+        <v>0.1573</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4173</v>
+        <v>0.1573</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6156</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1982</v>
+        <v>0.1573</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5288</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8806</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3519</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1115</v>
+        <v>0.1573</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2651</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8464</v>
+        <v>0.1573</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7578</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4065</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6487</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1573</v>
+        <v>-0.763</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.1341</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1573</v>
+        <v>-0.8971</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1573</v>
+        <v>-0.2436</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.8894</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1573</v>
+        <v>0.6458</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.2322</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.4671</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6993</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1573</v>
+        <v>-0.4759</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.4223</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>-0.0535</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.4472</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.0982</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.349</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.049</v>
+        <v>-1.1371</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0161</v>
+        <v>2.3421</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0651</v>
+        <v>-3.4792</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2436</v>
+        <v>0.4173</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8894</v>
+        <v>2.6156</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6458</v>
+        <v>-2.1982</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2322</v>
+        <v>1.5288</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4671</v>
+        <v>2.8806</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6993</v>
+        <v>-1.3519</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4759</v>
+        <v>-1.1115</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4223</v>
+        <v>-0.2651</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0535</v>
+        <v>-0.8464</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7332</v>
+        <v>-0.624</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2161</v>
+        <v>0.9911</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5171</v>
+        <v>-1.6151</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5361</v>
+        <v>-0.9304</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. SAMANIC</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.765</v>
+        <v>-4.7703</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6638</v>
+        <v>-2.2749</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1012</v>
+        <v>-2.4954</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0956</v>
+        <v>0.7496</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2797</v>
+        <v>-0.3275</v>
       </c>
       <c r="I10" t="n">
-        <v>0.184</v>
+        <v>1.0771</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4456</v>
+        <v>-0.0186</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1611</v>
+        <v>-0.3662</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2845</v>
+        <v>0.3476</v>
       </c>
       <c r="M10" t="n">
-        <v>0.35</v>
+        <v>0.7682</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1186</v>
+        <v>0.0387</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4685</v>
+        <v>0.7296</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9735</v>
+        <v>-1.4477</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7389</v>
+        <v>0.0633</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2346</v>
+        <v>-1.511</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1444</v>
+        <v>-2.6805</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1444</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>L. SAMANIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0836</v>
+        <v>-5.4619</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2185</v>
+        <v>-4.4278</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8651</v>
+        <v>-1.034</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7496</v>
+        <v>-0.0956</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3275</v>
+        <v>-0.2797</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0771</v>
+        <v>0.184</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0186</v>
+        <v>-0.4456</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3662</v>
+        <v>-0.1611</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3476</v>
+        <v>-0.2845</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7682</v>
+        <v>0.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0387</v>
+        <v>-0.1186</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7296</v>
+        <v>0.4685</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R11" t="n">
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.761</v>
+        <v>-0.6704</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8804</v>
+        <v>-0.503</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8806</v>
+        <v>-0.1674</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.6805</v>
+        <v>-2.1444</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6805</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5868</v>
+        <v>-6.2837</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4408</v>
+        <v>-4.2049</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.146</v>
+        <v>-2.0788</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9153</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2618</v>
+        <v>0.0413</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2082</v>
+        <v>0.0277</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0536</v>
+        <v>0.0136</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4665</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.249599999999999</v>
+        <v>-9.249499999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>6.443899999999998</v>
+        <v>6.4442</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.6934</v>
+        <v>-15.6935</v>
       </c>
       <c r="G13" t="n">
         <v>11.2532</v>
@@ -1447,7 +1447,7 @@
         <v>6.5286</v>
       </c>
       <c r="L13" t="n">
-        <v>7.1587</v>
+        <v>7.158700000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-2.4342</v>
@@ -1468,13 +1468,13 @@
         <v>11.5976</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.425400000000001</v>
+        <v>-5.4253</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2069</v>
+        <v>3.206999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-8.632199999999999</v>
+        <v>-8.632200000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-10.4384</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.1226</v>
+        <v>6.6247</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9003</v>
+        <v>5.6592</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2223</v>
+        <v>0.9656</v>
       </c>
       <c r="G14" t="n">
         <v>0.2972</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>5.8976</v>
+        <v>3.3997</v>
       </c>
       <c r="T14" t="n">
-        <v>4.9228</v>
+        <v>2.6817</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9748</v>
+        <v>0.718</v>
       </c>
       <c r="V14" t="n">
         <v>1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7372</v>
+        <v>6.2864</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5355</v>
+        <v>4.2996</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2017</v>
+        <v>1.9868</v>
       </c>
       <c r="G15" t="n">
         <v>2.7579</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8918</v>
+        <v>1.4409</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7774</v>
+        <v>1.5415</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-0.1006</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0085</v>
+        <v>2.4596</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4812</v>
+        <v>2.3508</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5273</v>
+        <v>0.1088</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.8811</v>
+        <v>-2.8076</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8095</v>
+        <v>0.6589</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.0716</v>
+        <v>-3.4664</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.6913</v>
+        <v>-1.007</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3656</v>
+        <v>0.7667</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.3257</v>
+        <v>-1.7737</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1898</v>
+        <v>-1.8006</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4439</v>
+        <v>-0.1078</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7459</v>
+        <v>-1.6928</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0876</v>
+        <v>2.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9049</v>
+        <v>1.6768</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2754</v>
+        <v>1.4787</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.1981</v>
       </c>
       <c r="V16" t="n">
-        <v>3.2166</v>
+        <v>3.3584</v>
       </c>
       <c r="W16" t="n">
-        <v>3.2166</v>
+        <v>4.4306</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5266</v>
+        <v>2.3938</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2959</v>
+        <v>1.3466</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7693</v>
+        <v>1.0472</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0988</v>
+        <v>-1.9434</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8114</v>
+        <v>2.4164</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9102</v>
+        <v>-4.3598</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0684</v>
+        <v>-1.1755</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8907</v>
+        <v>2.0201</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1778</v>
+        <v>-3.1956</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9696</v>
+        <v>-0.7678</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7021</v>
+        <v>0.3963</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2676</v>
+        <v>-1.1642</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3249</v>
+        <v>1.8527</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5975</v>
+        <v>1.5375</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7275</v>
+        <v>0.3152</v>
       </c>
       <c r="V17" t="n">
-        <v>3.2166</v>
+        <v>1.3247</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2166</v>
+        <v>2.1444</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3707</v>
+        <v>1.8309</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9354</v>
+        <v>0.5376</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5647</v>
+        <v>1.2934</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8076</v>
+        <v>-3.8811</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6589</v>
+        <v>-0.8095</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.4664</v>
+        <v>-3.0716</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.007</v>
+        <v>-2.6913</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7667</v>
+        <v>-0.3656</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.7737</v>
+        <v>-2.3257</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8006</v>
+        <v>-1.1898</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1078</v>
+        <v>-0.4439</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6928</v>
+        <v>-0.7459</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7834</v>
+        <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4121</v>
+        <v>2.7274</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0633</v>
+        <v>2.3318</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4753</v>
+        <v>0.3956</v>
       </c>
       <c r="V18" t="n">
-        <v>3.3584</v>
+        <v>3.2166</v>
       </c>
       <c r="W18" t="n">
-        <v>4.4306</v>
+        <v>3.2166</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4021</v>
+        <v>1.6445</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5406</v>
+        <v>3.4138</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1385</v>
+        <v>-1.7693</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9434</v>
+        <v>0.0988</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4164</v>
+        <v>-0.8114</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.3598</v>
+        <v>0.9102</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1755</v>
+        <v>2.0684</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0201</v>
+        <v>0.8907</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.1956</v>
+        <v>1.1778</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7678</v>
+        <v>-1.9696</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3963</v>
+        <v>-1.7021</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1642</v>
+        <v>-0.2676</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9432</v>
+        <v>-1.207</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3497</v>
+        <v>-0.4795</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5935</v>
+        <v>-0.7275</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3247</v>
+        <v>3.2166</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1444</v>
+        <v>3.2166</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7384</v>
+        <v>-1.604</v>
       </c>
       <c r="E20" t="n">
         <v>-0.9683</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7701</v>
+        <v>-0.6357</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8335</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.673</v>
+        <v>-0.5386</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2908</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3822</v>
+        <v>-0.2478</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4389</v>
+        <v>-1.6754</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2756</v>
+        <v>0.7474</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7145</v>
+        <v>-2.4228</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1472</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4514</v>
+        <v>-0.6879</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4402</v>
+        <v>0.0316</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0113</v>
+        <v>-0.7196</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7567</v>
+        <v>-3.0712</v>
       </c>
       <c r="E22" t="n">
-        <v>0.925</v>
+        <v>0.4532</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6817</v>
+        <v>-3.5245</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5376</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3066</v>
+        <v>-0.6212</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4208</v>
+        <v>-0.051</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7275</v>
+        <v>-0.5702</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1799</v>
+        <v>-3.2807</v>
       </c>
       <c r="E23" t="n">
         <v>-2.1464</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0335</v>
+        <v>-1.1343</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2567</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1577</v>
+        <v>-0.2585</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0083</v>
+        <v>-0.1092</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6778999999999999</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.249599999999999</v>
+        <v>11.6086</v>
       </c>
       <c r="E24" t="n">
-        <v>15.6936</v>
+        <v>15.6935</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.444000000000001</v>
+        <v>-4.0848</v>
       </c>
       <c r="G24" t="n">
         <v>-11.2532</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0357</v>
+        <v>-2.035699999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-9.217400000000001</v>
@@ -2314,7 +2314,7 @@
         <v>-6.528599999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.1588</v>
+        <v>-7.158799999999999</v>
       </c>
       <c r="P24" t="n">
         <v>4.6391</v>
@@ -2326,13 +2326,13 @@
         <v>16.2367</v>
       </c>
       <c r="S24" t="n">
-        <v>5.425399999999998</v>
+        <v>7.784300000000002</v>
       </c>
       <c r="T24" t="n">
         <v>8.632099999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.2069</v>
+        <v>-0.8480000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>10.4384</v>
